--- a/www/download/IND.surplus_value.empe_ms.r.pc.rpPE.xlsx
+++ b/www/download/IND.surplus_value.empe_ms.r.pc.rpPE.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Petrovic</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-40.91</t>
+          <t>-0.40909134023827</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-46.16</t>
+          <t>-0.461634208446697</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-46.12</t>
+          <t>-0.46117755084837</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-38.61</t>
+          <t>-0.386083298458668</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-39.23</t>
+          <t>-0.392261425830453</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-35.52</t>
+          <t>-0.355180883267561</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-32.11</t>
+          <t>-0.321119749356741</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-35.92</t>
+          <t>-0.359178437154741</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>-45.86</t>
+          <t>-0.458573997540574</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-49.65</t>
+          <t>-0.496544897737119</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>-50.84</t>
+          <t>-0.508419550357012</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>-51.43</t>
+          <t>-0.51425138477935</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-53.84</t>
+          <t>-0.538441043004989</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-51.15</t>
+          <t>-0.511467779505932</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-49.96</t>
+          <t>-0.499555011356784</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-64.46</t>
+          <t>-0.644583249982523</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-62.66</t>
+          <t>-0.62657086455863</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-58.11</t>
+          <t>-0.581063359109052</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-59.1</t>
+          <t>-0.591033610348008</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-56.29</t>
+          <t>-0.562893144822545</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-51.15</t>
+          <t>-0.511541582134663</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-51.28</t>
+          <t>-0.512778162904015</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-54.03</t>
+          <t>-0.540310984519992</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>-58.95</t>
+          <t>-0.589479842443479</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-60.2</t>
+          <t>-0.602024693192409</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>-59.7</t>
+          <t>-0.596996818017862</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>-59.8</t>
+          <t>-0.597976344590318</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>-60.44</t>
+          <t>-0.604429914119521</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>-61.3</t>
+          <t>-0.613002053449716</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>-62.09</t>
+          <t>-0.620885399526865</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-69.48</t>
+          <t>-0.694770149754517</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-68.35</t>
+          <t>-0.683484334650554</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-65.24</t>
+          <t>-0.65238652333989</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-65.83</t>
+          <t>-0.658250609701474</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-63.95</t>
+          <t>-0.639519299602348</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-59.65</t>
+          <t>-0.596546908457939</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-60.87</t>
+          <t>-0.608745219510564</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-63.97</t>
+          <t>-0.639717104220993</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>-68.06</t>
+          <t>-0.680551724508375</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-69.61</t>
+          <t>-0.696141267677207</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>-68.61</t>
+          <t>-0.686084975330373</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>-68.38</t>
+          <t>-0.683774344072436</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>-68.98</t>
+          <t>-0.689845470897404</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>-69.53</t>
+          <t>-0.695340646446326</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>-70.33</t>
+          <t>-0.703317870814382</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>635.98</t>
+          <t>6.35983677527213</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>735.21</t>
+          <t>7.35206522551627</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>938.51</t>
+          <t>9.38507765882273</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>590.22</t>
+          <t>5.902218049604</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>596.8</t>
+          <t>5.96798174044035</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>608.71</t>
+          <t>6.08711647153703</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>521.38</t>
+          <t>5.21381417341837</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>467.21</t>
+          <t>4.67210968044306</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>540.82</t>
+          <t>5.4082033007502</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>345.94</t>
+          <t>3.45941434131165</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>341.01</t>
+          <t>3.41007519738007</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>328.25</t>
+          <t>3.28252635388237</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>287.6</t>
+          <t>2.87596932715841</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>229.21</t>
+          <t>2.29214431876491</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>203.3</t>
+          <t>2.03295665832449</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>153.47</t>
+          <t>1.53467551920246</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>139.42</t>
+          <t>1.39422288598785</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>144.39</t>
+          <t>1.443903025513</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>151.49</t>
+          <t>1.51494892725147</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>304.84</t>
+          <t>3.04838705421525</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>303.8</t>
+          <t>3.03801119908317</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>375.52</t>
+          <t>3.75522397926874</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>462.18</t>
+          <t>4.62183364731118</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>482.09</t>
+          <t>4.82089486155103</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>468.34</t>
+          <t>4.6833749570476</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>359.4</t>
+          <t>3.59398565986528</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>305.15</t>
+          <t>3.05150489151024</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>275.45</t>
+          <t>2.75449279385182</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>245.91</t>
+          <t>2.45908796825651</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>232.2</t>
+          <t>2.32203569725385</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-31.6</t>
+          <t>-0.315996678271479</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>-31.57</t>
+          <t>-0.315698056523231</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>-34.34</t>
+          <t>-0.343418043252117</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-32.73</t>
+          <t>-0.32733704629962</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-31.62</t>
+          <t>-0.316154795692539</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-35.91</t>
+          <t>-0.359060225592672</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-36.46</t>
+          <t>-0.364569679307152</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-36</t>
+          <t>-0.359977817393227</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>-42.31</t>
+          <t>-0.423134378696351</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-43.09</t>
+          <t>-0.430908557506068</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>-46.71</t>
+          <t>-0.467108837326218</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>-50.05</t>
+          <t>-0.500469055234588</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>-48.77</t>
+          <t>-0.487682735424114</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>-47.53</t>
+          <t>-0.475283184720782</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>-45.94</t>
+          <t>-0.459366337891697</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>737.35</t>
+          <t>7.37346111645029</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>651.84</t>
+          <t>6.51844679906784</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>565.99</t>
+          <t>5.65991094093777</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>517.97</t>
+          <t>5.1796978139236</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>506.95</t>
+          <t>5.06954840032314</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>465.22</t>
+          <t>4.65218035108413</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>458.94</t>
+          <t>4.58937053595415</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>460.46</t>
+          <t>4.60460038614668</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>468.48</t>
+          <t>4.68482162938598</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>483.22</t>
+          <t>4.83216017142372</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>462.3</t>
+          <t>4.62302465578878</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>411.33</t>
+          <t>4.11328186054814</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>391.97</t>
+          <t>3.91967811569559</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>338.31</t>
+          <t>3.38306041722228</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>294.55</t>
+          <t>2.94550968088386</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.00554625174316103</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.00232044240620144</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.00419923811562128</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-4.13</t>
+          <t>-0.0412988983706686</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>0.0135454597270417</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>0.0972736584401741</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>5.28</t>
+          <t>0.0527567403488989</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>-0.036899030705724</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>-18.33</t>
+          <t>-0.183311023786331</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-24.61</t>
+          <t>-0.246053761564579</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>-24.23</t>
+          <t>-0.242252210359535</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>-21.16</t>
+          <t>-0.211617077973035</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>-19.34</t>
+          <t>-0.193363825943425</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>-19.57</t>
+          <t>-0.195678030184447</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>-20.54</t>
+          <t>-0.205377960375564</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>365.48</t>
+          <t>3.65480783080925</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>214.04</t>
+          <t>2.1403571854676</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>227.78</t>
+          <t>2.27777618057938</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>203.81</t>
+          <t>2.03807589184997</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>220.74</t>
+          <t>2.20744825152258</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>233.53</t>
+          <t>2.33527437435799</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>185.19</t>
+          <t>1.8519337028391</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>128.71</t>
+          <t>1.28711239129433</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>89.91</t>
+          <t>0.899107267685861</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>81.89</t>
+          <t>0.818905077953332</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>72.59</t>
+          <t>0.725922622557985</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>61.2</t>
+          <t>0.612032971205015</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>52.07</t>
+          <t>0.520727055635874</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>30.73</t>
+          <t>0.307302831022318</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>42.46</t>
+          <t>0.424556986946378</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-64.01</t>
+          <t>-0.640103913703207</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>-63.03</t>
+          <t>-0.630319731479175</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>-59.1</t>
+          <t>-0.591021558736812</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-59.21</t>
+          <t>-0.592068973535919</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-57.22</t>
+          <t>-0.572163046112235</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-52.89</t>
+          <t>-0.528911317955194</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-53.57</t>
+          <t>-0.535677824083658</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-55.67</t>
+          <t>-0.556655992765265</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>-61.41</t>
+          <t>-0.61412924970453</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-62.24</t>
+          <t>-0.622420794271994</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>-60.44</t>
+          <t>-0.604414411332314</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>-59.12</t>
+          <t>-0.591240774632004</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>-57.98</t>
+          <t>-0.579835790053046</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>-58.69</t>
+          <t>-0.586938065113383</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>-60.11</t>
+          <t>-0.601091336840517</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-65.26</t>
+          <t>-0.652583541556753</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>-65.47</t>
+          <t>-0.654726828525845</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>-62.22</t>
+          <t>-0.62220408808925</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-63.21</t>
+          <t>-0.632114847693016</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-61.29</t>
+          <t>-0.612929517755725</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-56.83</t>
+          <t>-0.568334432104274</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-57.9</t>
+          <t>-0.578970487012773</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-61.25</t>
+          <t>-0.612508774026059</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>-67.74</t>
+          <t>-0.677351896277205</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-68.88</t>
+          <t>-0.688818746337864</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>-68.43</t>
+          <t>-0.684340585824394</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>-68.43</t>
+          <t>-0.684305232911566</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>-69.08</t>
+          <t>-0.690828701225898</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>-69.53</t>
+          <t>-0.695310414337714</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>-70.82</t>
+          <t>-0.70818883770591</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-41.71</t>
+          <t>-0.417081180983975</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>-41.48</t>
+          <t>-0.414821965990692</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>-35</t>
+          <t>-0.350006456962168</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-35.52</t>
+          <t>-0.355209891447194</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-30.87</t>
+          <t>-0.308731808910633</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-22.53</t>
+          <t>-0.225314438053865</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-24.18</t>
+          <t>-0.241773514079062</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-29.24</t>
+          <t>-0.292427469874434</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>-35.21</t>
+          <t>-0.352056167068656</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-42.48</t>
+          <t>-0.424794701553773</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>-41.55</t>
+          <t>-0.415453604896019</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>-42</t>
+          <t>-0.420042622308616</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>-43.04</t>
+          <t>-0.430400292190029</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>-45.84</t>
+          <t>-0.458408294344314</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>-47.44</t>
+          <t>-0.474350677324447</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>535.47</t>
+          <t>5.35468778462598</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>417.02</t>
+          <t>4.17015640199503</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>377.85</t>
+          <t>3.77848424854944</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>319.83</t>
+          <t>3.19832996703582</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>325.25</t>
+          <t>3.25246858268407</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>324.51</t>
+          <t>3.24513302985606</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>284.74</t>
+          <t>2.84736235839854</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>237.07</t>
+          <t>2.37071145287134</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>163.73</t>
+          <t>1.63730240529065</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>133.84</t>
+          <t>1.33843949244926</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>127.9</t>
+          <t>1.27903530784614</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>107.04</t>
+          <t>1.07042120563315</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>64.92</t>
+          <t>0.64922625749342</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>46.72</t>
+          <t>0.467164247479846</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>39.24</t>
+          <t>0.392353125650135</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-53.72</t>
+          <t>-0.537174617599527</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>-52.49</t>
+          <t>-0.524897792258654</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>-48.52</t>
+          <t>-0.485165112716824</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-50.46</t>
+          <t>-0.504557048541462</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-46.95</t>
+          <t>-0.469537883565529</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-41.9</t>
+          <t>-0.41901805367419</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-44.68</t>
+          <t>-0.446796014652441</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-47.73</t>
+          <t>-0.477320507925273</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>-55.79</t>
+          <t>-0.557911137426033</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-56.71</t>
+          <t>-0.567095780226551</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>-55.89</t>
+          <t>-0.558886524649311</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>-55.39</t>
+          <t>-0.553942363457278</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>-54.77</t>
+          <t>-0.547746942315159</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>-56.03</t>
+          <t>-0.560331772138211</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>-57.61</t>
+          <t>-0.576071984832962</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-60.57</t>
+          <t>-0.605676330007156</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>-59.81</t>
+          <t>-0.598138401807012</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>-56.71</t>
+          <t>-0.56713839448844</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-57.41</t>
+          <t>-0.574079317800831</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-54.85</t>
+          <t>-0.548464861313305</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-50.42</t>
+          <t>-0.504205181703523</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-51.25</t>
+          <t>-0.512465064327759</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-55.98</t>
+          <t>-0.559820904668872</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>-61.48</t>
+          <t>-0.614803501506074</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-64.05</t>
+          <t>-0.640536643043513</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>-63.34</t>
+          <t>-0.633351016818127</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>-63.87</t>
+          <t>-0.638701948515621</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>-63.31</t>
+          <t>-0.633102170437416</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>-63.64</t>
+          <t>-0.636386497960159</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>-63.66</t>
+          <t>-0.636554654359016</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-37.5</t>
+          <t>-0.375046375107121</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>-37.55</t>
+          <t>-0.375502984261027</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>-43.96</t>
+          <t>-0.439629665589049</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-48.62</t>
+          <t>-0.486239013963487</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-47.95</t>
+          <t>-0.479524952955342</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-47.58</t>
+          <t>-0.475796213302167</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-48.62</t>
+          <t>-0.486160443436992</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-51.88</t>
+          <t>-0.518774149480013</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>-56.18</t>
+          <t>-0.561847261845395</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-59.15</t>
+          <t>-0.591474602795403</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>-58.23</t>
+          <t>-0.582332887276855</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>-58.79</t>
+          <t>-0.58794000103286</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>-59.41</t>
+          <t>-0.594148025427281</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>-53.06</t>
+          <t>-0.530555793641858</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>-49.4</t>
+          <t>-0.494031047935693</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>32.77</t>
+          <t>0.327707069039947</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>0.231517149200692</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>16.08</t>
+          <t>0.160791599567185</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>16.33</t>
+          <t>0.163344979716625</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>14.58</t>
+          <t>0.145786316846058</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>25.48</t>
+          <t>0.254815216027337</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>26.24</t>
+          <t>0.262449471907463</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>10.14</t>
+          <t>0.101413371386859</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>-5.37</t>
+          <t>-0.0537220013772329</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-13.5</t>
+          <t>-0.134961892711071</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>-13.54</t>
+          <t>-0.135449508448638</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>-11.17</t>
+          <t>-0.111725335583246</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>-16.25</t>
+          <t>-0.162515975814669</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>-19.04</t>
+          <t>-0.190405900978932</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>-26.02</t>
+          <t>-0.260159416099645</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>225.03</t>
+          <t>2.25033772949785</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>227.29</t>
+          <t>2.27292019139293</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>224.23</t>
+          <t>2.24233818242753</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>222.28</t>
+          <t>2.22278690644568</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>262.22</t>
+          <t>2.62216216603696</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>250.27</t>
+          <t>2.50270388672319</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>208.89</t>
+          <t>2.08892960633711</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>151.41</t>
+          <t>1.51408960890958</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>115.37</t>
+          <t>1.15370785227726</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>91.4</t>
+          <t>0.914041079348878</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>88.25</t>
+          <t>0.882477809428223</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>97.03</t>
+          <t>0.970325893404398</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>81.58</t>
+          <t>0.815820513327169</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>74.25</t>
+          <t>0.742509992672308</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>97.25</t>
+          <t>0.972509954415736</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>426.57</t>
+          <t>4.26574094256221</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>417.66</t>
+          <t>4.1765598100203</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>396.5</t>
+          <t>3.96500112240586</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1296.57</t>
+          <t>12.9657190208363</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1021.65</t>
+          <t>10.2164869604345</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>942.43</t>
+          <t>9.42428294866064</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>911.48</t>
+          <t>9.11483876571937</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>726.56</t>
+          <t>7.26559222888514</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>630.23</t>
+          <t>6.30229089314466</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>626.86</t>
+          <t>6.2686124888112</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>576.87</t>
+          <t>5.76872654792371</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>455.75</t>
+          <t>4.55753086572661</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>441.3</t>
+          <t>4.41301906574968</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>406.45</t>
+          <t>4.06445265683397</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>382.71</t>
+          <t>3.82711167636965</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2024.39</t>
+          <t>20.2438923612837</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2184.27</t>
+          <t>21.8427168752073</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1859.13</t>
+          <t>18.5913333009883</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1839.4</t>
+          <t>18.3940101195138</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1832.49</t>
+          <t>18.3249391839409</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>1897.73</t>
+          <t>18.9773125969665</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1918.17</t>
+          <t>19.1817425747124</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1920.67</t>
+          <t>19.2066798120969</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>1860.43</t>
+          <t>18.6042892292099</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>1829.51</t>
+          <t>18.2951488190166</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>1661.2</t>
+          <t>16.6120432392629</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>1530.34</t>
+          <t>15.3033635121942</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>1341.4</t>
+          <t>13.4140327827262</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>1351.2</t>
+          <t>13.5119740846294</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>1232.14</t>
+          <t>12.3214236708917</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-38.9</t>
+          <t>-0.388982881957824</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>-40.84</t>
+          <t>-0.408434487871489</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>-42.88</t>
+          <t>-0.428764438739044</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-42.99</t>
+          <t>-0.429949435104049</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-41.04</t>
+          <t>-0.41039293030004</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-38.3</t>
+          <t>-0.382962981506394</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-41.8</t>
+          <t>-0.418014747977026</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>-46.95</t>
+          <t>-0.46950412614361</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>-55.72</t>
+          <t>-0.557190870447075</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-58.39</t>
+          <t>-0.583949078011006</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>-55.99</t>
+          <t>-0.559909368262341</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>-54.98</t>
+          <t>-0.549830496462817</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>-55.29</t>
+          <t>-0.552925240051112</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>-60.13</t>
+          <t>-0.601306715242072</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>-60.66</t>
+          <t>-0.606635964790826</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-47.4</t>
+          <t>-0.474039959520258</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>-52.51</t>
+          <t>-0.525126680613771</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>-51.26</t>
+          <t>-0.512589892495916</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-50.06</t>
+          <t>-0.500600700890589</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-46.37</t>
+          <t>-0.463693140032911</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-38.88</t>
+          <t>-0.388772752743278</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>-43.01</t>
+          <t>-0.430083949919611</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>-47.44</t>
+          <t>-0.474406488060894</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>-51.33</t>
+          <t>-0.513283921255239</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-56.92</t>
+          <t>-0.569238276282285</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>-56.47</t>
+          <t>-0.564710147079925</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>-56.18</t>
+          <t>-0.561782398241044</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>-56.2</t>
+          <t>-0.562032477205746</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>-55.78</t>
+          <t>-0.557784911336369</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>-56.68</t>
+          <t>-0.566827229633039</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>-61.24</t>
+          <t>-0.612358300108422</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>-53.97</t>
+          <t>-0.539689843978672</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>-51.06</t>
+          <t>-0.510567548700313</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-47.95</t>
+          <t>-0.479505989915092</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-52.87</t>
+          <t>-0.528693198474534</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-55.81</t>
+          <t>-0.55814404911699</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>-50.87</t>
+          <t>-0.50874418027465</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>-47.67</t>
+          <t>-0.47673455247496</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>-48.81</t>
+          <t>-0.488128515100485</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-47.99</t>
+          <t>-0.479866330213434</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>-45.39</t>
+          <t>-0.453897137522751</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>-39.75</t>
+          <t>-0.397493606806131</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>-32.49</t>
+          <t>-0.324868274014759</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>-35.77</t>
+          <t>-0.357744929698309</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>-44.57</t>
+          <t>-0.445698599104027</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>47.25</t>
+          <t>0.472519106028268</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>34.52</t>
+          <t>0.345208855441251</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>44.84</t>
+          <t>0.44839384790339</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>106.6</t>
+          <t>1.06604368974942</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>81.94</t>
+          <t>0.819423717381969</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>61.76</t>
+          <t>0.617580507955156</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>72.45</t>
+          <t>0.724507422134774</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>55.92</t>
+          <t>0.559157940669553</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>43.89</t>
+          <t>0.438939254549281</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>49.45</t>
+          <t>0.494454781505218</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>32.61</t>
+          <t>0.326134468361127</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>23.97</t>
+          <t>0.239669194597888</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>24.83</t>
+          <t>0.248326541155979</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>49.78</t>
+          <t>0.497781746052108</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>60.29</t>
+          <t>0.602866706696061</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>820.87</t>
+          <t>8.20865559608208</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>596.47</t>
+          <t>5.96473676264086</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>451.48</t>
+          <t>4.51478867003951</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>380.7</t>
+          <t>3.80703961136416</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>380.9</t>
+          <t>3.8089738444475</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>408.25</t>
+          <t>4.08245985673168</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>357.19</t>
+          <t>3.5718651706936</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>303.39</t>
+          <t>3.03386317109992</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>2.16996359554948</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>190.12</t>
+          <t>1.90122334279473</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>1.82003352441301</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>149.35</t>
+          <t>1.49348517159306</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>123.9</t>
+          <t>1.2389665499611</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>101.82</t>
+          <t>1.01820221531979</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>127.27</t>
+          <t>1.27266944800977</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>-73.2</t>
+          <t>-0.731968757252496</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>-72.08</t>
+          <t>-0.720809159605335</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>-68.89</t>
+          <t>-0.688895386296046</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-68.36</t>
+          <t>-0.683588438918734</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-65.89</t>
+          <t>-0.658925128942536</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-62.44</t>
+          <t>-0.624431849310143</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>-63.79</t>
+          <t>-0.63789154426861</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>-66.2</t>
+          <t>-0.662048754825521</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>-69.01</t>
+          <t>-0.690118095051489</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-69.94</t>
+          <t>-0.699425099900642</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>-68.99</t>
+          <t>-0.6898811020266</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>-69.39</t>
+          <t>-0.693885081310216</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>-69.32</t>
+          <t>-0.693234152411339</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>-71.66</t>
+          <t>-0.716575190245422</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>-70.67</t>
+          <t>-0.706692966609031</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>572.27</t>
+          <t>5.72268565948136</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>444.55</t>
+          <t>4.44548356649799</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>404.09</t>
+          <t>4.04090357941871</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>391.82</t>
+          <t>3.91817974642887</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>376.02</t>
+          <t>3.76018375447314</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>365.33</t>
+          <t>3.65326694835899</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>334.8</t>
+          <t>3.34797997664652</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>311.02</t>
+          <t>3.11016093130127</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>249.4</t>
+          <t>2.49401784301772</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>221.19</t>
+          <t>2.21189601700977</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>180.63</t>
+          <t>1.80631448187478</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>134.02</t>
+          <t>1.34016964829599</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>0.7830085576679</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>57.83</t>
+          <t>0.578287527413568</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>88.63</t>
+          <t>0.886276685300516</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>228.05</t>
+          <t>2.28046745525006</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>217.97</t>
+          <t>2.17971728721013</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>170.88</t>
+          <t>1.70883258204202</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>151.98</t>
+          <t>1.51984220614595</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>135.95</t>
+          <t>1.3594839835364</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>100.84</t>
+          <t>1.00844775832891</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>0.821955259229482</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>80.83</t>
+          <t>0.808308449728099</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>104.93</t>
+          <t>1.04926728673927</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>133.34</t>
+          <t>1.33337906456549</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>122.04</t>
+          <t>1.22043556923679</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>125.07</t>
+          <t>1.25073670450985</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>138.88</t>
+          <t>1.38879416793575</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>1.59003120857049</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>198.78</t>
+          <t>1.98779294206061</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>25.43</t>
+          <t>0.254306595045285</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>19.24</t>
+          <t>0.192391747270681</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>18.37</t>
+          <t>0.18366697740047</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>11.41</t>
+          <t>0.114061594726557</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>13.82</t>
+          <t>0.13821215222682</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>18.43</t>
+          <t>0.184338312277557</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>-5.24</t>
+          <t>-0.0523959948178461</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>4.49</t>
+          <t>0.0448844799601507</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>19.19</t>
+          <t>0.191886006493292</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>-11.36</t>
+          <t>-0.113627455997533</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>-7.56</t>
+          <t>-0.075569557300181</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>-6.91</t>
+          <t>-0.0691407435799243</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>-4.22</t>
+          <t>-0.0422154815962821</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>-12.32</t>
+          <t>-0.12317256693918</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>-12.7</t>
+          <t>-0.126982369627044</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>-62.47</t>
+          <t>-0.624731527482828</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>-61.27</t>
+          <t>-0.612741311215963</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>-56.86</t>
+          <t>-0.568622422791132</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-58.79</t>
+          <t>-0.587883549894946</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-56.18</t>
+          <t>-0.561806463361101</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-53.47</t>
+          <t>-0.534704805738741</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>-55.46</t>
+          <t>-0.554630390764798</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>-58.92</t>
+          <t>-0.589232546956515</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>-63.36</t>
+          <t>-0.6335668747663</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-65.95</t>
+          <t>-0.659526479032931</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>-64.37</t>
+          <t>-0.643655616098756</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>-63.98</t>
+          <t>-0.639840484458125</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>-64.98</t>
+          <t>-0.649772519136581</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>-65.26</t>
+          <t>-0.652592779191018</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>-66.13</t>
+          <t>-0.661308346309487</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>178.22</t>
+          <t>1.78218948272267</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>139.48</t>
+          <t>1.39484831671226</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>132.12</t>
+          <t>1.32121806030253</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>108.32</t>
+          <t>1.08317850702745</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>131.16</t>
+          <t>1.31162051487611</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>139.55</t>
+          <t>1.39553978490337</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>125.83</t>
+          <t>1.2582909757093</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>125.69</t>
+          <t>1.25691956376977</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>124.59</t>
+          <t>1.24590715675536</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>130.77</t>
+          <t>1.30771389822216</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>111.33</t>
+          <t>1.1133097910274</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>109.04</t>
+          <t>1.09044427337517</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>99.82</t>
+          <t>0.998239508195049</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>67.48</t>
+          <t>0.674831769825742</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>97.81</t>
+          <t>0.978070578229931</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>-6.29</t>
+          <t>-0.0628749567318434</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>-10.53</t>
+          <t>-0.105291181353932</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>-10.15</t>
+          <t>-0.101509856006793</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-16.17</t>
+          <t>-0.161714059864744</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-10.97</t>
+          <t>-0.109668135087112</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-0.0327423509216774</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>-6.93</t>
+          <t>-0.069280568188712</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>-12.93</t>
+          <t>-0.129258140890364</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.00219623315197059</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>-25.3</t>
+          <t>-0.25303496915238</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>-24.15</t>
+          <t>-0.241502063285063</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>-19.67</t>
+          <t>-0.19667178266483</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>-18.43</t>
+          <t>-0.184320480430349</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>-19.49</t>
+          <t>-0.194898434284248</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>-20.37</t>
+          <t>-0.203692223055932</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>483.58</t>
+          <t>4.83578005933612</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>522.79</t>
+          <t>5.22786913233888</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>553.25</t>
+          <t>5.53247003346446</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>365.28</t>
+          <t>3.65277595931603</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>583.45</t>
+          <t>5.83452575901828</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>471.78</t>
+          <t>4.71781058161181</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>406.34</t>
+          <t>4.06338973722844</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>413.78</t>
+          <t>4.13783245066661</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>503.58</t>
+          <t>5.03576047944964</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>304.86</t>
+          <t>3.04863979327541</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>205.82</t>
+          <t>2.05818567325258</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>168.98</t>
+          <t>1.68984145724873</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>114.53</t>
+          <t>1.14529566668383</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>84.16</t>
+          <t>0.841610467341781</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>128.44</t>
+          <t>1.28439155083152</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>668.26</t>
+          <t>6.6826355490782</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>520.85</t>
+          <t>5.20846187779654</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>505.61</t>
+          <t>5.05609594056961</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>651.21</t>
+          <t>6.5120921522525</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>1242.29</t>
+          <t>12.4228529487935</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>929.26</t>
+          <t>9.29264942490199</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>761.38</t>
+          <t>7.61377631651906</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>651.81</t>
+          <t>6.5180913156077</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>549.24</t>
+          <t>5.49239195438128</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>438.84</t>
+          <t>4.38841450557353</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>364.85</t>
+          <t>3.64852790437347</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>280.23</t>
+          <t>2.8023076649221</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>222.4</t>
+          <t>2.22400962646751</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>156.14</t>
+          <t>1.56140380022453</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>216.06</t>
+          <t>2.16059716176307</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>486.43</t>
+          <t>4.86433862309717</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>431.47</t>
+          <t>4.31466639953017</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>378.14</t>
+          <t>3.78143051972709</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>343.67</t>
+          <t>3.43671222118156</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>410.7</t>
+          <t>4.10696306996449</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>394.6</t>
+          <t>3.94601483934088</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>374.79</t>
+          <t>3.74785057704657</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>300.34</t>
+          <t>3.00342339222318</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>208.06</t>
+          <t>2.08062239859108</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>179.08</t>
+          <t>1.79077822188146</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>168.3</t>
+          <t>1.6829823113145</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>145.9</t>
+          <t>1.45901258681185</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>109.34</t>
+          <t>1.0934135457474</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>81.51</t>
+          <t>0.81505923796184</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>65.35</t>
+          <t>0.653486576921448</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>15.33</t>
+          <t>0.153254863152179</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>16.68</t>
+          <t>0.166824461732302</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>17.93</t>
+          <t>0.179255513829235</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>12.23</t>
+          <t>0.122329665363093</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>17.14</t>
+          <t>0.171434676699037</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>32.08</t>
+          <t>0.320825989966574</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>23.21</t>
+          <t>0.232138000788201</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>14.74</t>
+          <t>0.147381319719043</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-0.0182467458819495</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>-6.92</t>
+          <t>-0.0692002270359232</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>-6.13</t>
+          <t>-0.0612566923998608</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>-8.37</t>
+          <t>-0.0837497541137965</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>-11.25</t>
+          <t>-0.112487050092837</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>-16.84</t>
+          <t>-0.168446182049353</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>-17.21</t>
+          <t>-0.172053130927061</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>-54.93</t>
+          <t>-0.549294688393719</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>-60.02</t>
+          <t>-0.600194164964859</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>-57.58</t>
+          <t>-0.575790939107231</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-57.76</t>
+          <t>-0.577626244222126</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-54.64</t>
+          <t>-0.546386727871516</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-54.04</t>
+          <t>-0.540415917089556</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>-52</t>
+          <t>-0.519953765723726</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>-55.93</t>
+          <t>-0.559309052062236</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>-63.14</t>
+          <t>-0.631386943230641</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>-64.37</t>
+          <t>-0.643688445889039</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>-63.05</t>
+          <t>-0.630504885174214</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>-62.61</t>
+          <t>-0.626060712360664</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>-62.96</t>
+          <t>-0.629570022780751</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>-61.17</t>
+          <t>-0.611684663323768</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>-57.87</t>
+          <t>-0.578659207222824</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>276.06</t>
+          <t>2.76056383726932</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>232.18</t>
+          <t>2.32180134680344</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>194.2</t>
+          <t>1.94202220049341</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>177.63</t>
+          <t>1.77626639175646</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>146.58</t>
+          <t>1.46577358798481</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>163.81</t>
+          <t>1.63813093971651</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>246.03</t>
+          <t>2.46026406839483</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>277.57</t>
+          <t>2.77572078392345</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>214.78</t>
+          <t>2.147751022867</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>162.47</t>
+          <t>1.62470246441915</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>134.74</t>
+          <t>1.34742214643515</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>126.59</t>
+          <t>1.26592655653117</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>1.03477811982491</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>97.75</t>
+          <t>0.9775300713292</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>124.39</t>
+          <t>1.24387917820131</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.00019069368403124</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>-4.38</t>
+          <t>-0.0437968102154622</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>-5.99</t>
+          <t>-0.0599022344118927</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>0.032376682889325</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>0.0192788919818137</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>-3.58</t>
+          <t>-0.0358071203844181</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-0.0221711060360181</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>0.0334551235785401</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>7.32</t>
+          <t>0.0732349776359038</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>14.74</t>
+          <t>0.147366980149398</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>13.64</t>
+          <t>0.136423509052672</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>18.08</t>
+          <t>0.180844624732169</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>33.15</t>
+          <t>0.331478662785508</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>42.3</t>
+          <t>0.42295844231045</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>42.55</t>
+          <t>0.425517424915685</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>-43.56</t>
+          <t>-0.435553531783412</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>-44.94</t>
+          <t>-0.449362104362832</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>-47.29</t>
+          <t>-0.472944478550278</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-50.11</t>
+          <t>-0.501139078270775</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-50.57</t>
+          <t>-0.505675308090192</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-52.53</t>
+          <t>-0.525291442976147</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>-55.67</t>
+          <t>-0.556742205040767</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>-56.97</t>
+          <t>-0.569687889748497</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>-56.98</t>
+          <t>-0.569806130752686</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>-54.05</t>
+          <t>-0.540491846963031</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>-53.5</t>
+          <t>-0.535015003707853</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>-52.46</t>
+          <t>-0.524558766819908</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>-49.72</t>
+          <t>-0.49718862407671</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>-47.01</t>
+          <t>-0.470068939437223</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>-50.08</t>
+          <t>-0.500788033157742</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>241.87</t>
+          <t>2.41868257876451</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>241.03</t>
+          <t>2.41025291164426</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>237.54</t>
+          <t>2.37539532336758</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>246.9</t>
+          <t>2.46904011956644</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>264.12</t>
+          <t>2.64116204704329</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>261.48</t>
+          <t>2.61481195326883</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>268.99</t>
+          <t>2.68993047329394</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>294.71</t>
+          <t>2.94710348622285</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>308.97</t>
+          <t>3.08966470130745</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>308.17</t>
+          <t>3.08165483482039</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>289.08</t>
+          <t>2.89075134021673</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>273.66</t>
+          <t>2.73662005250102</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>279.24</t>
+          <t>2.79240119002082</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>255.23</t>
+          <t>2.55231908334575</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>275.09</t>
+          <t>2.75085316454728</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>25.14</t>
+          <t>0.251394415438399</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>29.22</t>
+          <t>0.292222580871519</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>30.91</t>
+          <t>0.309140744546763</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>30.57</t>
+          <t>0.305653634679999</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>33.13</t>
+          <t>0.331329906898271</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>32.42</t>
+          <t>0.324170938074983</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>34.57</t>
+          <t>0.345714899109803</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>35.99</t>
+          <t>0.359874894817778</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>34.81</t>
+          <t>0.348072272129126</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>37.78</t>
+          <t>0.37783672609627</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>38.84</t>
+          <t>0.388366161904179</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>39.21</t>
+          <t>0.392106378694381</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>43.54</t>
+          <t>0.435388875501731</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>0.454961778521963</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>47.13</t>
+          <t>0.471318276761859</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4339,7 +4344,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4351,7 +4356,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4363,7 +4368,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4375,7 +4380,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4387,7 +4392,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4399,7 +4404,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4411,7 +4416,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4423,7 +4428,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4470,6 +4475,11 @@
           <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4504,6 +4514,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Petrovic</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpPE</t>
